--- a/DateBase/orders/Dang Nguyen 195_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-13.xlsx
@@ -524,7 +524,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>5</v>
+        <v>53</v>
+      </c>
+      <c r="C11" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-13.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,10 +529,81 @@
       <c r="C11" t="str">
         <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>54</v>
+      </c>
+      <c r="C13" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>55</v>
+      </c>
+      <c r="C15" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>56</v>
+      </c>
+      <c r="C16" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>111_绣球紫_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>57</v>
+      </c>
+      <c r="C18" t="str">
+        <v>111_绣球紫_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +658,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>081042820151523400</v>
+        <v>08104282015152340102929829136535</v>
       </c>
     </row>
   </sheetData>
